--- a/data/trans_orig/Q5410A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1899,62 +1899,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>579</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>442</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14233</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>401</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Clase-trans_orig.xlsx
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>639</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>639</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>381</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>487</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>840</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>313</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,22 +2851,22 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>991</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>405</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>372</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>365</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23825</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9652</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
